--- a/Output/Weekly Scan_19 Jul 2026.xlsx
+++ b/Output/Weekly Scan_19 Jul 2026.xlsx
@@ -19912,7 +19912,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19980,122 +19980,20 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>360ONE</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+          <t>No scanner alerts detected for this interval</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3A360ONE</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>BIOCON</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABIOCON</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>CONCOR</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ACONCOR</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>TORNTPHARM</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>High Vol Expansion</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ATORNTPHARM</t>
-        </is>
-      </c>
+      <c r="L2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
